--- a/28卒一日の流れ.xlsx
+++ b/28卒一日の流れ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacherM\Desktop\GitHub\GameEngine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A29D27-52C7-4A69-952B-3392C1FB895A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35794F42-3853-441F-AFF9-45A466B49C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="59">
   <si>
     <t>平日</t>
     <rPh sb="0" eb="2">
@@ -334,6 +334,146 @@
       <t>ハン</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勉強</t>
+    <rPh sb="0" eb="2">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ご飯</t>
+    <rPh sb="1" eb="2">
+      <t>ハン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自由</t>
+    <rPh sb="0" eb="2">
+      <t>ジユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ご飯</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家事</t>
+    <rPh sb="0" eb="2">
+      <t>カジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>買い出し</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>起床・ご飯</t>
+    <rPh sb="0" eb="2">
+      <t>キショウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ハン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>掃除</t>
+    <rPh sb="0" eb="2">
+      <t>ソウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家族サービス</t>
+    <rPh sb="0" eb="2">
+      <t>カゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム(1時まで)</t>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>起床・ご飯</t>
+    <rPh sb="4" eb="5">
+      <t>ハン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勉強or外出</t>
+    <rPh sb="0" eb="2">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕事</t>
+    <rPh sb="0" eb="2">
+      <t>シゴト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕事・帰宅</t>
+    <rPh sb="0" eb="2">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>帰宅・食事・風呂</t>
+    <rPh sb="0" eb="2">
+      <t>キタク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショクジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OW・勉強</t>
+    <rPh sb="3" eb="5">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OW・漫画・小説</t>
+    <rPh sb="3" eb="5">
+      <t>マンガ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショウセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風呂</t>
   </si>
 </sst>
 </file>
@@ -365,7 +505,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,6 +536,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -409,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -418,6 +564,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -698,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="6.75" customWidth="1"/>
@@ -722,7 +869,7 @@
     <col min="19" max="19" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1">
+    <row r="1" spans="1:21" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -755,7 +902,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:21">
       <c r="A2" s="1">
         <v>0.29166666666666669</v>
       </c>
@@ -786,8 +933,11 @@
       <c r="S2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="U2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="1">
         <v>0.33333333333333298</v>
       </c>
@@ -818,8 +968,11 @@
       <c r="S3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="U3" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="1">
         <v>0.375</v>
       </c>
@@ -850,8 +1003,11 @@
       <c r="S4" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="U4" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="1">
         <v>0.41666666666666702</v>
       </c>
@@ -882,8 +1038,11 @@
       <c r="S5" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="U5" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="1">
         <v>0.45833333333333298</v>
       </c>
@@ -914,8 +1073,11 @@
       <c r="S6" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="U6" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="1">
         <v>0.5</v>
       </c>
@@ -946,8 +1108,11 @@
       <c r="S7" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="U7" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="1">
         <v>0.54166666666666696</v>
       </c>
@@ -978,8 +1143,11 @@
       <c r="S8" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="U8" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="1">
         <v>0.58333333333333304</v>
       </c>
@@ -1010,8 +1178,11 @@
       <c r="S9" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="U9" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="1">
         <v>0.625</v>
       </c>
@@ -1042,8 +1213,11 @@
       <c r="S10" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="U10" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="1">
         <v>0.66666666666666696</v>
       </c>
@@ -1074,8 +1248,11 @@
       <c r="S11" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="U11" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="1">
         <v>0.70833333333333304</v>
       </c>
@@ -1106,8 +1283,11 @@
       <c r="S12" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="U12" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="1">
         <v>0.75</v>
       </c>
@@ -1138,8 +1318,11 @@
       <c r="S13" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="U13" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="1">
         <v>0.79166666666666696</v>
       </c>
@@ -1170,8 +1353,11 @@
       <c r="S14" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="U14" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="1">
         <v>0.83333333333333304</v>
       </c>
@@ -1202,8 +1388,11 @@
       <c r="S15" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="U15" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="1">
         <v>0.875</v>
       </c>
@@ -1234,8 +1423,11 @@
       <c r="S16" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:19">
+      <c r="U16" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="1">
         <v>0.91666666666666696</v>
       </c>
@@ -1266,8 +1458,11 @@
       <c r="S17" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="U17" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="1">
         <v>0.95833333333332804</v>
       </c>
@@ -1298,8 +1493,11 @@
       <c r="S18" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:19">
+      <c r="U18" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="1">
         <v>0.999999999999994</v>
       </c>
@@ -1330,10 +1528,594 @@
       <c r="S19" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" s="2" customFormat="1">
+      <c r="U19" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" s="2" customFormat="1">
       <c r="A21" s="3" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="1">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="1">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>51</v>
+      </c>
+      <c r="S23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="1">
+        <v>0.375</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S24" t="s">
+        <v>51</v>
+      </c>
+      <c r="U24" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="1">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" t="s">
+        <v>4</v>
+      </c>
+      <c r="M25" t="s">
+        <v>4</v>
+      </c>
+      <c r="O25" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" s="1">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M26" t="s">
+        <v>42</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" s="1">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>44</v>
+      </c>
+      <c r="S28" t="s">
+        <v>44</v>
+      </c>
+      <c r="U28" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" s="1">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O29" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>43</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" t="s">
+        <v>43</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I30" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O30" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>43</v>
+      </c>
+      <c r="S30" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" s="1">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I31" t="s">
+        <v>27</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O31" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>43</v>
+      </c>
+      <c r="S31" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" s="1">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I32" t="s">
+        <v>27</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O32" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>43</v>
+      </c>
+      <c r="S32" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" t="s">
+        <v>7</v>
+      </c>
+      <c r="O33" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>43</v>
+      </c>
+      <c r="S33" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" s="1">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" t="s">
+        <v>7</v>
+      </c>
+      <c r="M34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O34" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>43</v>
+      </c>
+      <c r="S34" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" s="1">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O35" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>44</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
+      <c r="A36" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>43</v>
+      </c>
+      <c r="S36" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U36" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" s="1">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M37" t="s">
+        <v>31</v>
+      </c>
+      <c r="O37" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>43</v>
+      </c>
+      <c r="S37" t="s">
+        <v>44</v>
+      </c>
+      <c r="U37" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" s="1">
+        <v>0.95833333333332804</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>43</v>
+      </c>
+      <c r="S38" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" s="1">
+        <v>0.999999999999994</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M39" t="s">
+        <v>32</v>
+      </c>
+      <c r="O39" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>7</v>
+      </c>
+      <c r="S39" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="U39" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="U40" s="6" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
